--- a/nr-cleaning/ig/StructureDefinition-as-dp-practitionerrole.xlsx
+++ b/nr-cleaning/ig/StructureDefinition-as-dp-practitionerrole.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4708" uniqueCount="631">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4707" uniqueCount="630">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-06T15:04:54+00:00</t>
+    <t>2024-03-06T15:16:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -647,13 +647,10 @@
 </t>
   </si>
   <si>
-    <t>Secteur de conventionnement du professionnel libéral auquel il a adhéré auprès de l'Assurance Maladie.</t>
+    <t>Secteur de conventionnement du professionnel libéral auquel il a adhéré auprès de l'Assurance Maladie (Synonyme : secteurConventionnement).</t>
   </si>
   <si>
     <t>Extension créée dans le cadre de l'Annuaire Santé pour décrire le secteur de conventionnement du professionnel libéral auquel il a adhéré auprès de l'Assurance Maladie.</t>
-  </si>
-  <si>
-    <t>Synonyme : secteurConventionnement</t>
   </si>
   <si>
     <t>PractitionerRole.extension:as-ext-practitionerrole-hascas</t>
@@ -4429,9 +4426,7 @@
       <c r="M19" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="N19" t="s" s="2">
-        <v>204</v>
-      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>77</v>
@@ -4509,13 +4504,13 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B20" t="s" s="2">
         <v>196</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>77</v>
@@ -4537,13 +4532,13 @@
         <v>77</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>209</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4623,13 +4618,13 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B21" t="s" s="2">
         <v>196</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>77</v>
@@ -4651,13 +4646,13 @@
         <v>77</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>214</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4737,10 +4732,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4766,16 +4761,16 @@
         <v>111</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="N22" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>77</v>
@@ -4824,7 +4819,7 @@
         <v>117</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4853,10 +4848,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4879,17 +4874,17 @@
         <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>77</v>
@@ -4926,10 +4921,10 @@
         <v>77</v>
       </c>
       <c r="AB23" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AC23" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>77</v>
@@ -4938,7 +4933,7 @@
         <v>117</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4953,27 +4948,27 @@
         <v>101</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AL23" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="AL23" t="s" s="2">
+      <c r="AM23" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="AM23" t="s" s="2">
+      <c r="AN23" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>230</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="C24" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="B24" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="C24" t="s" s="2">
-        <v>232</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>77</v>
@@ -4995,17 +4990,17 @@
         <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>77</v>
@@ -5054,7 +5049,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -5069,24 +5064,24 @@
         <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AL24" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="AL24" t="s" s="2">
+      <c r="AM24" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="AM24" t="s" s="2">
+      <c r="AN24" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>230</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="B25" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="B25" t="s" s="2">
-        <v>235</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5195,10 +5190,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="B26" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5309,10 +5304,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="B27" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5338,16 +5333,16 @@
         <v>173</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="N27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -5372,31 +5367,31 @@
         <v>77</v>
       </c>
       <c r="X27" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="Y27" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="Y27" t="s" s="2">
+      <c r="Z27" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="Z27" t="s" s="2">
+      <c r="AA27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF27" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="AA27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF27" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -5414,7 +5409,7 @@
         <v>102</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>77</v>
@@ -5425,10 +5420,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="B28" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="B28" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5451,19 +5446,19 @@
         <v>89</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="N28" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>255</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>77</v>
@@ -5491,28 +5486,28 @@
         <v>153</v>
       </c>
       <c r="Y28" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="Z28" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="Z28" t="s" s="2">
+      <c r="AA28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF28" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="AA28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF28" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5527,10 +5522,10 @@
         <v>101</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>
@@ -5541,10 +5536,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="B29" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5570,16 +5565,16 @@
         <v>137</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="N29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>77</v>
@@ -5589,46 +5584,46 @@
         <v>77</v>
       </c>
       <c r="S29" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="T29" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="T29" t="s" s="2">
+      <c r="U29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF29" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="U29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5643,13 +5638,13 @@
         <v>101</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="AL29" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="AL29" t="s" s="2">
+      <c r="AM29" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>77</v>
@@ -5657,10 +5652,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="B30" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="B30" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5686,13 +5681,13 @@
         <v>104</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5706,43 +5701,43 @@
         <v>77</v>
       </c>
       <c r="T30" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="U30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF30" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="U30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF30" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5757,13 +5752,13 @@
         <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AL30" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="AL30" t="s" s="2">
+      <c r="AM30" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>77</v>
@@ -5771,10 +5766,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="B31" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5797,16 +5792,16 @@
         <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5856,7 +5851,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5868,16 +5863,16 @@
         <v>100</v>
       </c>
       <c r="AJ31" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AK31" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="AK31" t="s" s="2">
+      <c r="AL31" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="AL31" t="s" s="2">
+      <c r="AM31" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>77</v>
@@ -5885,10 +5880,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="B32" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="B32" t="s" s="2">
-        <v>294</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5911,16 +5906,16 @@
         <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5970,7 +5965,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5982,16 +5977,16 @@
         <v>100</v>
       </c>
       <c r="AJ32" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AK32" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="AK32" t="s" s="2">
+      <c r="AL32" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="AL32" t="s" s="2">
+      <c r="AM32" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>303</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>77</v>
@@ -5999,13 +5994,13 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="C33" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="C33" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="D33" t="s" s="2">
         <v>77</v>
@@ -6027,17 +6022,17 @@
         <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>77</v>
@@ -6086,7 +6081,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -6101,24 +6096,24 @@
         <v>101</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AL33" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="AL33" t="s" s="2">
+      <c r="AM33" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="AM33" t="s" s="2">
+      <c r="AN33" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>230</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6227,10 +6222,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6341,10 +6336,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6370,16 +6365,16 @@
         <v>173</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="N36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -6404,31 +6399,31 @@
         <v>77</v>
       </c>
       <c r="X36" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="Y36" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="Y36" t="s" s="2">
+      <c r="Z36" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="Z36" t="s" s="2">
+      <c r="AA36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF36" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="AA36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF36" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6446,7 +6441,7 @@
         <v>102</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>77</v>
@@ -6457,10 +6452,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6483,19 +6478,19 @@
         <v>89</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="N37" t="s" s="2">
+      <c r="O37" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>255</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>77</v>
@@ -6523,28 +6518,28 @@
         <v>153</v>
       </c>
       <c r="Y37" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="Z37" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="Z37" t="s" s="2">
+      <c r="AA37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF37" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="AA37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF37" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6559,10 +6554,10 @@
         <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>77</v>
@@ -6573,10 +6568,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6602,16 +6597,16 @@
         <v>137</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="N38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>77</v>
@@ -6621,46 +6616,46 @@
         <v>77</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="T38" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF38" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="U38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF38" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6675,13 +6670,13 @@
         <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="AL38" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="AL38" t="s" s="2">
+      <c r="AM38" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>77</v>
@@ -6689,10 +6684,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6718,13 +6713,13 @@
         <v>104</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6738,43 +6733,43 @@
         <v>77</v>
       </c>
       <c r="T39" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="U39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF39" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="U39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF39" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6789,13 +6784,13 @@
         <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AL39" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="AL39" t="s" s="2">
+      <c r="AM39" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>77</v>
@@ -6803,10 +6798,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6829,16 +6824,16 @@
         <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6888,7 +6883,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6900,16 +6895,16 @@
         <v>100</v>
       </c>
       <c r="AJ40" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AK40" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="AK40" t="s" s="2">
+      <c r="AL40" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="AL40" t="s" s="2">
+      <c r="AM40" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>77</v>
@@ -6917,10 +6912,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6943,16 +6938,16 @@
         <v>89</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7002,7 +6997,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -7014,16 +7009,16 @@
         <v>100</v>
       </c>
       <c r="AJ41" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AK41" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="AK41" t="s" s="2">
+      <c r="AL41" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="AL41" t="s" s="2">
+      <c r="AM41" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>303</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>77</v>
@@ -7031,10 +7026,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7057,26 +7052,26 @@
         <v>89</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="N42" t="s" s="2">
+      <c r="O42" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="O42" t="s" s="2">
+      <c r="P42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q42" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="P42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q42" t="s" s="2">
-        <v>322</v>
-      </c>
       <c r="R42" t="s" s="2">
         <v>77</v>
       </c>
@@ -7120,7 +7115,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -7135,24 +7130,24 @@
         <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="AL42" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="AL42" t="s" s="2">
+      <c r="AM42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN42" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>325</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7175,19 +7170,19 @@
         <v>89</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="O43" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>77</v>
@@ -7236,7 +7231,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -7248,27 +7243,27 @@
         <v>100</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AL43" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="AL43" t="s" s="2">
+      <c r="AM43" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="AM43" t="s" s="2">
+      <c r="AN43" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>333</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7377,10 +7372,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7491,10 +7486,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7517,16 +7512,16 @@
         <v>89</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7576,25 +7571,25 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI46" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="AG46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH46" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI46" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="AL46" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>344</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>77</v>
@@ -7605,10 +7600,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7631,69 +7626,69 @@
         <v>89</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>348</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q47" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="R47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF47" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="R47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF47" t="s" s="2">
-        <v>350</v>
-      </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
       </c>
@@ -7701,16 +7696,16 @@
         <v>88</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK47" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="AL47" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="AL47" t="s" s="2">
-        <v>352</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>77</v>
@@ -7721,10 +7716,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7747,16 +7742,16 @@
         <v>89</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7806,7 +7801,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7818,13 +7813,13 @@
         <v>100</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>77</v>
@@ -7835,10 +7830,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7861,16 +7856,16 @@
         <v>89</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="M49" t="s" s="2">
-        <v>362</v>
-      </c>
       <c r="N49" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7920,7 +7915,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7932,13 +7927,13 @@
         <v>100</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>77</v>
@@ -7949,10 +7944,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7975,19 +7970,19 @@
         <v>89</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="N50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>77</v>
@@ -8015,16 +8010,16 @@
         <v>163</v>
       </c>
       <c r="Y50" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="Z50" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="Z50" t="s" s="2">
+      <c r="AA50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB50" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>371</v>
       </c>
       <c r="AC50" s="2"/>
       <c r="AD50" t="s" s="2">
@@ -8034,7 +8029,7 @@
         <v>117</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -8049,13 +8044,13 @@
         <v>101</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AL50" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AL50" t="s" s="2">
-        <v>373</v>
-      </c>
       <c r="AM50" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>77</v>
@@ -8063,13 +8058,13 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="C51" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="C51" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>77</v>
@@ -8091,19 +8086,19 @@
         <v>89</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="M51" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="N51" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="N51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>77</v>
@@ -8128,11 +8123,11 @@
         <v>77</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>77</v>
@@ -8150,7 +8145,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -8165,13 +8160,13 @@
         <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AL51" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AL51" t="s" s="2">
-        <v>373</v>
-      </c>
       <c r="AM51" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>77</v>
@@ -8179,13 +8174,13 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="C52" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="B52" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="C52" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="D52" t="s" s="2">
         <v>77</v>
@@ -8207,19 +8202,19 @@
         <v>89</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="M52" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="N52" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="N52" t="s" s="2">
+      <c r="O52" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>77</v>
@@ -8244,11 +8239,11 @@
         <v>77</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Y52" s="2"/>
       <c r="Z52" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>77</v>
@@ -8266,7 +8261,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8281,13 +8276,13 @@
         <v>101</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AL52" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AL52" t="s" s="2">
-        <v>373</v>
-      </c>
       <c r="AM52" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>77</v>
@@ -8295,13 +8290,13 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="C53" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="C53" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="D53" t="s" s="2">
         <v>77</v>
@@ -8323,19 +8318,19 @@
         <v>89</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="M53" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="N53" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="N53" t="s" s="2">
+      <c r="O53" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>77</v>
@@ -8360,11 +8355,11 @@
         <v>77</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>77</v>
@@ -8382,7 +8377,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8397,13 +8392,13 @@
         <v>101</v>
       </c>
       <c r="AK53" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AL53" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AL53" t="s" s="2">
-        <v>373</v>
-      </c>
       <c r="AM53" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>77</v>
@@ -8411,13 +8406,13 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="C54" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="B54" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="C54" t="s" s="2">
-        <v>387</v>
       </c>
       <c r="D54" t="s" s="2">
         <v>77</v>
@@ -8439,19 +8434,19 @@
         <v>89</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="M54" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="N54" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="N54" t="s" s="2">
+      <c r="O54" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>77</v>
@@ -8476,11 +8471,11 @@
         <v>77</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Y54" s="2"/>
       <c r="Z54" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>77</v>
@@ -8498,7 +8493,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8513,13 +8508,13 @@
         <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AL54" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AL54" t="s" s="2">
-        <v>373</v>
-      </c>
       <c r="AM54" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>77</v>
@@ -8527,13 +8522,13 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="C55" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="B55" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="C55" t="s" s="2">
-        <v>391</v>
       </c>
       <c r="D55" t="s" s="2">
         <v>77</v>
@@ -8555,19 +8550,19 @@
         <v>89</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="M55" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="N55" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="N55" t="s" s="2">
+      <c r="O55" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>77</v>
@@ -8592,11 +8587,11 @@
         <v>77</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>77</v>
@@ -8614,7 +8609,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8629,13 +8624,13 @@
         <v>101</v>
       </c>
       <c r="AK55" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AL55" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AL55" t="s" s="2">
-        <v>373</v>
-      </c>
       <c r="AM55" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>77</v>
@@ -8643,13 +8638,13 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="C56" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="B56" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="C56" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>77</v>
@@ -8671,19 +8666,19 @@
         <v>89</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="M56" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="N56" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="N56" t="s" s="2">
+      <c r="O56" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>77</v>
@@ -8708,11 +8703,11 @@
         <v>77</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>77</v>
@@ -8730,7 +8725,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8745,13 +8740,13 @@
         <v>101</v>
       </c>
       <c r="AK56" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AL56" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AL56" t="s" s="2">
-        <v>373</v>
-      </c>
       <c r="AM56" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>77</v>
@@ -8759,13 +8754,13 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="C57" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="B57" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="C57" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="D57" t="s" s="2">
         <v>77</v>
@@ -8787,19 +8782,19 @@
         <v>89</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="M57" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="N57" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="N57" t="s" s="2">
+      <c r="O57" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>77</v>
@@ -8824,11 +8819,11 @@
         <v>77</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>77</v>
@@ -8846,7 +8841,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8861,13 +8856,13 @@
         <v>101</v>
       </c>
       <c r="AK57" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AL57" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AL57" t="s" s="2">
-        <v>373</v>
-      </c>
       <c r="AM57" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>77</v>
@@ -8875,10 +8870,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8901,16 +8896,16 @@
         <v>89</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8939,11 +8934,11 @@
         <v>177</v>
       </c>
       <c r="Y58" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="Z58" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="Z58" t="s" s="2">
-        <v>407</v>
-      </c>
       <c r="AA58" t="s" s="2">
         <v>77</v>
       </c>
@@ -8960,7 +8955,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8975,13 +8970,13 @@
         <v>101</v>
       </c>
       <c r="AK58" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AL58" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="AL58" t="s" s="2">
+      <c r="AM58" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>77</v>
@@ -8989,10 +8984,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9015,16 +9010,16 @@
         <v>89</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="M59" t="s" s="2">
-        <v>414</v>
-      </c>
       <c r="N59" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9074,7 +9069,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -9086,27 +9081,27 @@
         <v>100</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL59" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="AM59" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="AM59" t="s" s="2">
+      <c r="AN59" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>417</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9129,16 +9124,16 @@
         <v>77</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="M60" t="s" s="2">
-        <v>421</v>
-      </c>
       <c r="N60" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9188,7 +9183,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -9200,13 +9195,13 @@
         <v>100</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AK60" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AL60" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>77</v>
@@ -9217,10 +9212,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9243,17 +9238,17 @@
         <v>89</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>427</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>77</v>
@@ -9290,17 +9285,17 @@
         <v>77</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AC61" s="2"/>
       <c r="AD61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -9312,16 +9307,16 @@
         <v>100</v>
       </c>
       <c r="AJ61" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AK61" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="AK61" t="s" s="2">
+      <c r="AL61" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="AL61" t="s" s="2">
+      <c r="AM61" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>434</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>77</v>
@@ -9329,13 +9324,13 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="C62" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="C62" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="D62" t="s" s="2">
         <v>77</v>
@@ -9357,17 +9352,17 @@
         <v>77</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>77</v>
@@ -9416,7 +9411,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9428,16 +9423,16 @@
         <v>100</v>
       </c>
       <c r="AJ62" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AK62" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="AK62" t="s" s="2">
-        <v>432</v>
-      </c>
       <c r="AL62" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>77</v>
@@ -9445,10 +9440,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="B63" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>442</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9557,10 +9552,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="B64" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>444</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9671,13 +9666,13 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="C65" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="C65" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="D65" t="s" s="2">
         <v>77</v>
@@ -9699,13 +9694,13 @@
         <v>77</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="L65" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="L65" t="s" s="2">
+      <c r="M65" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>449</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9785,10 +9780,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="B66" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="B66" t="s" s="2">
-        <v>451</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9897,10 +9892,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="B67" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9926,10 +9921,10 @@
         <v>111</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>455</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10009,10 +10004,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="B68" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10038,13 +10033,13 @@
         <v>137</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="N68" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10052,49 +10047,49 @@
       </c>
       <c r="Q68" s="2"/>
       <c r="R68" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF68" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="S68" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T68" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U68" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V68" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W68" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X68" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y68" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z68" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA68" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>88</v>
@@ -10123,10 +10118,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="B69" t="s" s="2">
         <v>463</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10152,10 +10147,10 @@
         <v>149</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>466</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10167,7 +10162,7 @@
         <v>77</v>
       </c>
       <c r="S69" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="T69" t="s" s="2">
         <v>77</v>
@@ -10186,25 +10181,25 @@
       </c>
       <c r="Y69" s="2"/>
       <c r="Z69" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF69" t="s" s="2">
         <v>468</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>469</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10233,13 +10228,13 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="C70" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="B70" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="C70" t="s" s="2">
-        <v>471</v>
       </c>
       <c r="D70" t="s" s="2">
         <v>77</v>
@@ -10261,13 +10256,13 @@
         <v>77</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="L70" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="L70" t="s" s="2">
+      <c r="M70" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>474</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10347,10 +10342,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10459,10 +10454,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10573,13 +10568,13 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="C73" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="C73" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="D73" t="s" s="2">
         <v>77</v>
@@ -10604,10 +10599,10 @@
         <v>111</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10687,10 +10682,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="B74" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="B74" t="s" s="2">
-        <v>481</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10799,10 +10794,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="B75" t="s" s="2">
         <v>482</v>
-      </c>
-      <c r="B75" t="s" s="2">
-        <v>483</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10828,10 +10823,10 @@
         <v>111</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>455</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10911,10 +10906,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="B76" t="s" s="2">
         <v>484</v>
-      </c>
-      <c r="B76" t="s" s="2">
-        <v>485</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10940,13 +10935,13 @@
         <v>137</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="N76" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -10954,7 +10949,7 @@
       </c>
       <c r="Q76" s="2"/>
       <c r="R76" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="S76" t="s" s="2">
         <v>77</v>
@@ -10996,7 +10991,7 @@
         <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>88</v>
@@ -11025,10 +11020,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="B77" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>487</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11051,13 +11046,13 @@
         <v>77</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>466</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11084,11 +11079,11 @@
         <v>77</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Y77" s="2"/>
       <c r="Z77" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>77</v>
@@ -11106,7 +11101,7 @@
         <v>77</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -11135,13 +11130,13 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="C78" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="B78" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="C78" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="D78" t="s" s="2">
         <v>77</v>
@@ -11166,10 +11161,10 @@
         <v>111</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11249,10 +11244,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11361,10 +11356,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11390,10 +11385,10 @@
         <v>111</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>455</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11473,10 +11468,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11502,13 +11497,13 @@
         <v>137</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="M81" t="s" s="2">
+      <c r="N81" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11516,7 +11511,7 @@
       </c>
       <c r="Q81" s="2"/>
       <c r="R81" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="S81" t="s" s="2">
         <v>77</v>
@@ -11558,7 +11553,7 @@
         <v>77</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>88</v>
@@ -11587,10 +11582,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11616,10 +11611,10 @@
         <v>104</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="M82" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>466</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -11670,7 +11665,7 @@
         <v>77</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -11699,13 +11694,13 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="C83" t="s" s="2">
         <v>496</v>
-      </c>
-      <c r="B83" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="C83" t="s" s="2">
-        <v>497</v>
       </c>
       <c r="D83" t="s" s="2">
         <v>77</v>
@@ -11730,10 +11725,10 @@
         <v>111</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>455</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -11813,10 +11808,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11925,10 +11920,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11954,10 +11949,10 @@
         <v>111</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>455</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12037,10 +12032,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12066,13 +12061,13 @@
         <v>137</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="M86" t="s" s="2">
+      <c r="N86" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12080,7 +12075,7 @@
       </c>
       <c r="Q86" s="2"/>
       <c r="R86" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="S86" t="s" s="2">
         <v>77</v>
@@ -12122,7 +12117,7 @@
         <v>77</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>88</v>
@@ -12151,10 +12146,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12180,10 +12175,10 @@
         <v>104</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>466</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12234,7 +12229,7 @@
         <v>77</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -12263,13 +12258,13 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="C88" t="s" s="2">
         <v>502</v>
-      </c>
-      <c r="B88" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="C88" t="s" s="2">
-        <v>503</v>
       </c>
       <c r="D88" t="s" s="2">
         <v>77</v>
@@ -12294,10 +12289,10 @@
         <v>111</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12377,10 +12372,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12489,10 +12484,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12518,10 +12513,10 @@
         <v>111</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="M90" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>455</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -12601,10 +12596,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12630,13 +12625,13 @@
         <v>137</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="N91" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -12644,7 +12639,7 @@
       </c>
       <c r="Q91" s="2"/>
       <c r="R91" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="S91" t="s" s="2">
         <v>77</v>
@@ -12686,7 +12681,7 @@
         <v>77</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>88</v>
@@ -12715,10 +12710,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12744,10 +12739,10 @@
         <v>104</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="M92" t="s" s="2">
-        <v>466</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -12798,7 +12793,7 @@
         <v>77</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -12827,13 +12822,13 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="C93" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="B93" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="C93" t="s" s="2">
-        <v>510</v>
       </c>
       <c r="D93" t="s" s="2">
         <v>77</v>
@@ -12858,10 +12853,10 @@
         <v>111</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>455</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -12941,10 +12936,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13053,10 +13048,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13082,10 +13077,10 @@
         <v>111</v>
       </c>
       <c r="L95" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="M95" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>455</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -13165,10 +13160,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13194,13 +13189,13 @@
         <v>137</v>
       </c>
       <c r="L96" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="M96" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="M96" t="s" s="2">
+      <c r="N96" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -13208,7 +13203,7 @@
       </c>
       <c r="Q96" s="2"/>
       <c r="R96" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="S96" t="s" s="2">
         <v>77</v>
@@ -13250,7 +13245,7 @@
         <v>77</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>88</v>
@@ -13279,10 +13274,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13308,10 +13303,10 @@
         <v>104</v>
       </c>
       <c r="L97" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="M97" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>466</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -13362,7 +13357,7 @@
         <v>77</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
@@ -13391,13 +13386,13 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="C98" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="B98" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="C98" t="s" s="2">
-        <v>516</v>
       </c>
       <c r="D98" t="s" s="2">
         <v>77</v>
@@ -13422,10 +13417,10 @@
         <v>111</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -13505,10 +13500,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13617,10 +13612,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13646,10 +13641,10 @@
         <v>111</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="M100" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="M100" t="s" s="2">
-        <v>455</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -13729,10 +13724,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13758,13 +13753,13 @@
         <v>137</v>
       </c>
       <c r="L101" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="M101" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="M101" t="s" s="2">
+      <c r="N101" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -13772,7 +13767,7 @@
       </c>
       <c r="Q101" s="2"/>
       <c r="R101" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="S101" t="s" s="2">
         <v>77</v>
@@ -13814,7 +13809,7 @@
         <v>77</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>88</v>
@@ -13843,10 +13838,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13869,13 +13864,13 @@
         <v>77</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="L102" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="M102" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="M102" t="s" s="2">
-        <v>466</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -13926,7 +13921,7 @@
         <v>77</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
@@ -13955,13 +13950,13 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="C103" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="B103" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="C103" t="s" s="2">
-        <v>523</v>
       </c>
       <c r="D103" t="s" s="2">
         <v>77</v>
@@ -13986,10 +13981,10 @@
         <v>111</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -14069,10 +14064,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14181,10 +14176,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14210,10 +14205,10 @@
         <v>111</v>
       </c>
       <c r="L105" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="M105" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="M105" t="s" s="2">
-        <v>455</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -14293,10 +14288,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14322,13 +14317,13 @@
         <v>137</v>
       </c>
       <c r="L106" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="M106" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="M106" t="s" s="2">
+      <c r="N106" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -14336,7 +14331,7 @@
       </c>
       <c r="Q106" s="2"/>
       <c r="R106" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="S106" t="s" s="2">
         <v>77</v>
@@ -14378,7 +14373,7 @@
         <v>77</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>88</v>
@@ -14407,10 +14402,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14433,13 +14428,13 @@
         <v>77</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="L107" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="M107" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="M107" t="s" s="2">
-        <v>466</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -14490,7 +14485,7 @@
         <v>77</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>78</v>
@@ -14519,10 +14514,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14548,13 +14543,13 @@
         <v>137</v>
       </c>
       <c r="L108" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="M108" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="M108" t="s" s="2">
+      <c r="N108" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -14562,7 +14557,7 @@
       </c>
       <c r="Q108" s="2"/>
       <c r="R108" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="S108" t="s" s="2">
         <v>77</v>
@@ -14604,7 +14599,7 @@
         <v>77</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>88</v>
@@ -14633,10 +14628,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14659,13 +14654,13 @@
         <v>77</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="L109" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="M109" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="M109" t="s" s="2">
-        <v>466</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -14716,7 +14711,7 @@
         <v>77</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>78</v>
@@ -14745,10 +14740,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="B110" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="B110" t="s" s="2">
-        <v>534</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14774,13 +14769,13 @@
         <v>173</v>
       </c>
       <c r="L110" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="M110" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="M110" t="s" s="2">
+      <c r="N110" t="s" s="2">
         <v>536</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>537</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -14791,67 +14786,67 @@
         <v>77</v>
       </c>
       <c r="S110" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="T110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X110" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="Y110" t="s" s="2">
         <v>538</v>
       </c>
-      <c r="T110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X110" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="Y110" t="s" s="2">
+      <c r="Z110" t="s" s="2">
         <v>539</v>
       </c>
-      <c r="Z110" t="s" s="2">
+      <c r="AA110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF110" t="s" s="2">
         <v>540</v>
       </c>
-      <c r="AA110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF110" t="s" s="2">
+      <c r="AG110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH110" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI110" t="s" s="2">
         <v>541</v>
-      </c>
-      <c r="AG110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH110" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI110" t="s" s="2">
-        <v>542</v>
       </c>
       <c r="AJ110" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK110" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="AL110" t="s" s="2">
         <v>543</v>
       </c>
-      <c r="AL110" t="s" s="2">
+      <c r="AM110" t="s" s="2">
         <v>544</v>
-      </c>
-      <c r="AM110" t="s" s="2">
-        <v>545</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>77</v>
@@ -14859,10 +14854,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="B111" t="s" s="2">
         <v>546</v>
-      </c>
-      <c r="B111" t="s" s="2">
-        <v>547</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14888,16 +14883,16 @@
         <v>104</v>
       </c>
       <c r="L111" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="M111" t="s" s="2">
         <v>548</v>
       </c>
-      <c r="M111" t="s" s="2">
+      <c r="N111" t="s" s="2">
         <v>549</v>
       </c>
-      <c r="N111" t="s" s="2">
+      <c r="O111" t="s" s="2">
         <v>550</v>
-      </c>
-      <c r="O111" t="s" s="2">
-        <v>551</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>77</v>
@@ -14946,7 +14941,7 @@
         <v>77</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>78</v>
@@ -14961,13 +14956,13 @@
         <v>101</v>
       </c>
       <c r="AK111" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="AL111" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="AL111" t="s" s="2">
-        <v>554</v>
-      </c>
       <c r="AM111" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>77</v>
@@ -14975,10 +14970,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="B112" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="B112" t="s" s="2">
-        <v>556</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15004,16 +14999,16 @@
         <v>173</v>
       </c>
       <c r="L112" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="M112" t="s" s="2">
         <v>557</v>
       </c>
-      <c r="M112" t="s" s="2">
+      <c r="N112" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="N112" t="s" s="2">
+      <c r="O112" t="s" s="2">
         <v>559</v>
-      </c>
-      <c r="O112" t="s" s="2">
-        <v>560</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>77</v>
@@ -15038,31 +15033,31 @@
         <v>77</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Y112" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="Z112" t="s" s="2">
         <v>561</v>
       </c>
-      <c r="Z112" t="s" s="2">
+      <c r="AA112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF112" t="s" s="2">
         <v>562</v>
-      </c>
-      <c r="AA112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF112" t="s" s="2">
-        <v>563</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>78</v>
@@ -15077,13 +15072,13 @@
         <v>101</v>
       </c>
       <c r="AK112" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="AL112" t="s" s="2">
         <v>564</v>
       </c>
-      <c r="AL112" t="s" s="2">
+      <c r="AM112" t="s" s="2">
         <v>565</v>
-      </c>
-      <c r="AM112" t="s" s="2">
-        <v>566</v>
       </c>
       <c r="AN112" t="s" s="2">
         <v>77</v>
@@ -15091,10 +15086,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="B113" t="s" s="2">
         <v>567</v>
-      </c>
-      <c r="B113" t="s" s="2">
-        <v>568</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15117,16 +15112,16 @@
         <v>89</v>
       </c>
       <c r="K113" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="L113" t="s" s="2">
         <v>569</v>
       </c>
-      <c r="L113" t="s" s="2">
+      <c r="M113" t="s" s="2">
         <v>570</v>
       </c>
-      <c r="M113" t="s" s="2">
+      <c r="N113" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>572</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -15176,7 +15171,7 @@
         <v>77</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>78</v>
@@ -15205,10 +15200,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="B114" t="s" s="2">
         <v>574</v>
-      </c>
-      <c r="B114" t="s" s="2">
-        <v>575</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15231,16 +15226,16 @@
         <v>89</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="L114" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="M114" t="s" s="2">
         <v>576</v>
       </c>
-      <c r="M114" t="s" s="2">
-        <v>577</v>
-      </c>
       <c r="N114" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -15290,7 +15285,7 @@
         <v>77</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>78</v>
@@ -15302,16 +15297,16 @@
         <v>100</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AK114" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>77</v>
@@ -15319,10 +15314,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15345,16 +15340,16 @@
         <v>77</v>
       </c>
       <c r="K115" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="L115" t="s" s="2">
         <v>581</v>
       </c>
-      <c r="L115" t="s" s="2">
+      <c r="M115" t="s" s="2">
         <v>582</v>
       </c>
-      <c r="M115" t="s" s="2">
+      <c r="N115" t="s" s="2">
         <v>583</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>584</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -15404,7 +15399,7 @@
         <v>77</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>78</v>
@@ -15422,7 +15417,7 @@
         <v>77</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="AM115" t="s" s="2">
         <v>77</v>
@@ -15433,10 +15428,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15545,10 +15540,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15659,14 +15654,14 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
@@ -15688,16 +15683,16 @@
         <v>111</v>
       </c>
       <c r="L118" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="M118" t="s" s="2">
         <v>590</v>
-      </c>
-      <c r="M118" t="s" s="2">
-        <v>591</v>
       </c>
       <c r="N118" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O118" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>77</v>
@@ -15746,7 +15741,7 @@
         <v>77</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>78</v>
@@ -15775,10 +15770,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -15804,13 +15799,13 @@
         <v>173</v>
       </c>
       <c r="L119" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="M119" t="s" s="2">
         <v>594</v>
       </c>
-      <c r="M119" t="s" s="2">
-        <v>595</v>
-      </c>
       <c r="N119" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -15836,14 +15831,14 @@
         <v>77</v>
       </c>
       <c r="X119" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Y119" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="Z119" t="s" s="2">
         <v>596</v>
       </c>
-      <c r="Z119" t="s" s="2">
-        <v>597</v>
-      </c>
       <c r="AA119" t="s" s="2">
         <v>77</v>
       </c>
@@ -15860,7 +15855,7 @@
         <v>77</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>78</v>
@@ -15878,7 +15873,7 @@
         <v>77</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>77</v>
@@ -15889,10 +15884,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15915,13 +15910,13 @@
         <v>77</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="L120" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="M120" t="s" s="2">
         <v>599</v>
-      </c>
-      <c r="M120" t="s" s="2">
-        <v>600</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -15972,7 +15967,7 @@
         <v>77</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>78</v>
@@ -15990,7 +15985,7 @@
         <v>77</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>77</v>
@@ -16001,10 +15996,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16027,16 +16022,16 @@
         <v>77</v>
       </c>
       <c r="K121" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="L121" t="s" s="2">
         <v>602</v>
       </c>
-      <c r="L121" t="s" s="2">
+      <c r="M121" t="s" s="2">
         <v>603</v>
       </c>
-      <c r="M121" t="s" s="2">
+      <c r="N121" t="s" s="2">
         <v>604</v>
-      </c>
-      <c r="N121" t="s" s="2">
-        <v>605</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -16086,7 +16081,7 @@
         <v>77</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>78</v>
@@ -16104,7 +16099,7 @@
         <v>77</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>77</v>
@@ -16115,10 +16110,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16141,16 +16136,16 @@
         <v>77</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="L122" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="M122" t="s" s="2">
         <v>607</v>
       </c>
-      <c r="M122" t="s" s="2">
-        <v>608</v>
-      </c>
       <c r="N122" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
@@ -16200,7 +16195,7 @@
         <v>77</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>78</v>
@@ -16218,7 +16213,7 @@
         <v>77</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>77</v>
@@ -16229,10 +16224,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16255,13 +16250,13 @@
         <v>77</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="L123" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="M123" t="s" s="2">
         <v>610</v>
-      </c>
-      <c r="M123" t="s" s="2">
-        <v>611</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
@@ -16312,7 +16307,7 @@
         <v>77</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>78</v>
@@ -16330,7 +16325,7 @@
         <v>77</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="AM123" t="s" s="2">
         <v>77</v>
@@ -16341,10 +16336,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16453,10 +16448,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16567,14 +16562,14 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E126" s="2"/>
       <c r="F126" t="s" s="2">
@@ -16596,16 +16591,16 @@
         <v>111</v>
       </c>
       <c r="L126" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="M126" t="s" s="2">
         <v>590</v>
-      </c>
-      <c r="M126" t="s" s="2">
-        <v>591</v>
       </c>
       <c r="N126" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>77</v>
@@ -16654,7 +16649,7 @@
         <v>77</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>78</v>
@@ -16683,10 +16678,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -16712,13 +16707,13 @@
         <v>104</v>
       </c>
       <c r="L127" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="M127" t="s" s="2">
         <v>616</v>
       </c>
-      <c r="M127" t="s" s="2">
-        <v>617</v>
-      </c>
       <c r="N127" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
@@ -16768,7 +16763,7 @@
         <v>77</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>88</v>
@@ -16797,10 +16792,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -16823,16 +16818,16 @@
         <v>77</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="L128" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="M128" t="s" s="2">
         <v>619</v>
       </c>
-      <c r="M128" t="s" s="2">
-        <v>620</v>
-      </c>
       <c r="N128" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
@@ -16882,7 +16877,7 @@
         <v>77</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>78</v>
@@ -16894,13 +16889,13 @@
         <v>100</v>
       </c>
       <c r="AJ128" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="AM128" t="s" s="2">
         <v>77</v>
@@ -16911,10 +16906,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -16940,13 +16935,13 @@
         <v>104</v>
       </c>
       <c r="L129" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="M129" t="s" s="2">
         <v>623</v>
       </c>
-      <c r="M129" t="s" s="2">
-        <v>624</v>
-      </c>
       <c r="N129" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
@@ -16996,7 +16991,7 @@
         <v>77</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>78</v>
@@ -17014,7 +17009,7 @@
         <v>77</v>
       </c>
       <c r="AL129" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="AM129" t="s" s="2">
         <v>77</v>
@@ -17025,10 +17020,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17051,19 +17046,19 @@
         <v>77</v>
       </c>
       <c r="K130" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="L130" t="s" s="2">
         <v>626</v>
       </c>
-      <c r="L130" t="s" s="2">
+      <c r="M130" t="s" s="2">
         <v>627</v>
       </c>
-      <c r="M130" t="s" s="2">
+      <c r="N130" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="O130" t="s" s="2">
         <v>628</v>
-      </c>
-      <c r="N130" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="O130" t="s" s="2">
-        <v>629</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>77</v>
@@ -17112,7 +17107,7 @@
         <v>77</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>78</v>
@@ -17124,13 +17119,13 @@
         <v>100</v>
       </c>
       <c r="AJ130" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AK130" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL130" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="AM130" t="s" s="2">
         <v>77</v>

--- a/nr-cleaning/ig/StructureDefinition-as-dp-practitionerrole.xlsx
+++ b/nr-cleaning/ig/StructureDefinition-as-dp-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-06T15:16:55+00:00</t>
+    <t>2024-03-06T15:26:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-cleaning/ig/StructureDefinition-as-dp-practitionerrole.xlsx
+++ b/nr-cleaning/ig/StructureDefinition-as-dp-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-06T15:26:05+00:00</t>
+    <t>2024-03-06T16:31:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
